--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,27 +523,27 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-453</t>
+          <t>SM-455</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-452</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3983</v>
+        <v>4040</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4094</v>
+        <v>7884</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-111</v>
+        <v>-3844</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,27 +568,27 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>SM-453</t>
+          <t>SM-455</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-450</t>
+          <t>Nile Air NP-529</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3983</v>
+        <v>4082</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4094</v>
+        <v>7884</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-111</v>
+        <v>-3802</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -613,27 +613,27 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>SM-491</t>
+          <t>SM-455</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-452</t>
+          <t>Nile Air NP-629</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6740</v>
+        <v>4082</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7512</v>
+        <v>7884</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-772</v>
+        <v>-3802</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -658,27 +658,27 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>27-MAR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-953</t>
+          <t>SM-455</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-452</t>
+          <t>Nile Air NP-627</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6740</v>
+        <v>4082</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7044</v>
+        <v>7884</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-304</v>
+        <v>-3802</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -703,7 +703,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-530</t>
+          <t>Nile Air NP-427</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>5059</v>
+        <v>4082</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6575</v>
+        <v>7884</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1516</v>
+        <v>-3802</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -748,7 +748,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -758,17 +758,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-578</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>5059</v>
+        <v>4082</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6575</v>
+        <v>7884</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-1516</v>
+        <v>-3802</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -793,7 +793,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>01-APR-26</t>
+          <t>30-MAR-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-576</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5059</v>
+        <v>4082</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6575</v>
+        <v>7884</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-1516</v>
+        <v>-3802</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -838,7 +838,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-578</t>
+          <t>Nesma Airlines NE-178</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>3983</v>
+        <v>4040</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>6575</v>
+        <v>6930</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-2592</v>
+        <v>-2890</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -883,7 +883,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-APR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -893,17 +893,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-576</t>
+          <t>Nesma Airlines NE-970</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>3983</v>
+        <v>4040</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>6575</v>
+        <v>6930</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-2592</v>
+        <v>-2890</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -928,7 +928,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -938,26 +938,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6286</v>
+        <v>4082</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>7044</v>
+        <v>6930</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-758</v>
+        <v>-2848</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -983,26 +983,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>Nile Air NP-329</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6286</v>
+        <v>4082</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>7044</v>
+        <v>6930</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-758</v>
+        <v>-2848</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>04-APR-26</t>
+          <t>31-MAR-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1028,33 +1028,663 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nile Air NP-527</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6396</v>
+        <v>4082</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>7044</v>
+        <v>6930</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-648</v>
+        <v>-2848</v>
       </c>
       <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-327</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>4082</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>6930</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-2848</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>31-MAR-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>4082</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>6930</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-2848</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-530</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>5120</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>6158</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-1038</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-578</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>5120</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>6158</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-1038</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>01-APR-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-576</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5120</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>6158</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-1038</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-578</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>6242</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>7407</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-1165</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>03-APR-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-576</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>6242</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>7407</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-1165</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>05-APR-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-174</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>4040</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>6930</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-2890</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>06-APR-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>6369</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>7407</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-1038</v>
+      </c>
+      <c r="G22" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-669</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6369</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>6930</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-561</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>11-MAY-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-574</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>6860</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>9680</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-2820</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>11-MAY-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-584</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>6860</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>9680</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-2820</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>11-MAY-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-570</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>6860</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>9680</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-2820</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>11-MAY-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-572</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>6860</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>9680</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-2820</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>30-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4040</v>
+        <v>5044</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7884</v>
+        <v>8919</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3844</v>
+        <v>-3875</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -568,7 +568,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>30-MAR-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -578,17 +578,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-529</t>
+          <t>Nesma Airlines NE-176</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4082</v>
+        <v>5058</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7884</v>
+        <v>8919</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3802</v>
+        <v>-3861</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -605,546 +605,6 @@
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>30-MAR-26</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-629</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>4082</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>7884</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>-3802</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>30-MAR-26</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-627</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>4082</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>7884</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>-3802</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30-MAR-26</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-427</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>4082</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>7884</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>-3802</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>30-MAR-26</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-127</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>4082</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>7884</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>-3802</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>01-APR-26</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-530</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>5120</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>6158</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>-1038</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>01-APR-26</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-578</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>5120</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>6158</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>-1038</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>01-APR-26</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-576</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>5120</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>6158</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>-1038</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>03-APR-26</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-578</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>6242</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>7407</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>-1165</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>03-APR-26</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-576</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>6242</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>7407</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>-1165</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H12" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>05-APR-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-174</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>4040</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>6930</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-2890</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>06-APR-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-669</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>6369</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>7407</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-1038</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>07-APR-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-669</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>6369</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>6930</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-561</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW THREAT</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -459,7 +459,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -556,7 +556,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -610,6 +610,51 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>21-MAY-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5058</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>8919</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-3861</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>5044</v>
+        <v>4992</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>8919</v>
+        <v>8827</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3875</v>
+        <v>-3835</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>5058</v>
+        <v>5006</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8919</v>
+        <v>8827</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3861</v>
+        <v>-3821</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -627,13 +627,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>5058</v>
+        <v>5006</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>8919</v>
+        <v>8827</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3861</v>
+        <v>-3821</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -650,6 +650,231 @@
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-778</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>6261</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-4700</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>-3236</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-172</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>7725</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>-3236</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7739</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-3222</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>10514</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10961</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-447</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>4317</v>
+        <v>3722</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>7488</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3171</v>
+        <v>-3766</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>4317</v>
+        <v>3722</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>7488</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3171</v>
+        <v>-3766</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>21-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nile Air NP-327</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>4374</v>
+        <v>3892</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>7488</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3114</v>
+        <v>-3596</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6384</v>
+        <v>7856</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>11084</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-4700</v>
+        <v>-3228</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>7375</v>
+        <v>6228</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>11084</v>
+        <v>16718</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-3709</v>
+        <v>-10490</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +797,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-778</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>8054</v>
+        <v>6228</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>16718</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-8664</v>
+        <v>-10490</v>
       </c>
       <c r="G8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -866,28 +866,28 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>8281</v>
+        <v>6384</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>16718</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-8437</v>
+        <v>-10334</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>8281</v>
+        <v>6228</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>16718</v>
+        <v>13419</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-8437</v>
+        <v>-7191</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>8281</v>
+        <v>6228</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>16718</v>
+        <v>13419</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-8437</v>
+        <v>-7191</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6228</v>
+        <v>6384</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>13419</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7191</v>
+        <v>-7035</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,867 +1022,12 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-172</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>6228</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>-7191</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H13" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>04-JUN-26</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>8394</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>-5025</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H14" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-673</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>-5138</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>-5138</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H16" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>-5138</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H17" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>07-JUN-26</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-778</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>8622</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>13419</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>-4797</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>-3878</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>-3878</v>
-      </c>
-      <c r="G20" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H20" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>08-JUN-26</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-655</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>-3878</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H21" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-170</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>6228</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>-5931</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-227</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>6384</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>-5775</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H23" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>09-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-127</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>6384</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-5775</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-778</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>7206</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-4953</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>20</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-643</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>-3878</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H26" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J26" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>-3878</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H27" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>10-JUN-26</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-665</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>12159</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>-3878</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H28" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Nesma Airlines NE-176</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>6228</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>9583</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>-3355</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H29" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Nile Air NP-127</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>6384</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>9583</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>-3199</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H30" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>8281</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>9583</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>-1302</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>3722</v>
+        <v>6214</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7488</v>
+        <v>11076</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-3766</v>
+        <v>-4862</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>3722</v>
+        <v>7821</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7488</v>
+        <v>11076</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3766</v>
+        <v>-3255</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>30</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>29-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-327</t>
+          <t>flynas XY-568</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>3892</v>
+        <v>8638</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7488</v>
+        <v>11076</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3596</v>
+        <v>-2438</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6228</v>
+        <v>6214</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>11084</v>
+        <v>16699</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-4856</v>
+        <v>-10485</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>7856</v>
+        <v>6214</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>11084</v>
+        <v>16699</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-3228</v>
+        <v>-10485</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>30</v>
@@ -752,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6228</v>
+        <v>6355</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16718</v>
+        <v>16699</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-10490</v>
+        <v>-10344</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6228</v>
+        <v>5792</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>16718</v>
+        <v>13402</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-10490</v>
+        <v>-7610</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6384</v>
+        <v>6355</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>16718</v>
+        <v>13402</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-10334</v>
+        <v>-7047</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6228</v>
+        <v>6355</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13419</v>
+        <v>13402</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-7191</v>
+        <v>-7047</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6228</v>
+        <v>6214</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13419</v>
+        <v>13402</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-7191</v>
+        <v>-7188</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6384</v>
+        <v>6214</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13419</v>
+        <v>13402</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7035</v>
+        <v>-7188</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1028,6 +1028,591 @@
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>07-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-127</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>13402</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-7047</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-170</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-5933</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Nile Air NP-227</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>6355</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-5792</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>09-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-655</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>10-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-665</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>12147</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>-3889</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Nesma Airlines NE-176</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>6214</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>9568</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-3354</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-643</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>9568</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-1310</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>EGP</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>11-JUN-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-455</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-641</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>8258</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>9568</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-1310</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -470,7 +470,7 @@
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -596,26 +596,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Air Arabia Egypt E5-327</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>7821</v>
+        <v>6632</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11076</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-3255</v>
+        <v>-4444</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-568</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>8638</v>
+        <v>7821</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>11076</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2438</v>
+        <v>-3255</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>16699</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-10344</v>
+        <v>-8441</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
@@ -821,26 +821,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-673</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5792</v>
+        <v>6214</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>13402</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-7610</v>
+        <v>-7188</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6355</v>
+        <v>6214</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>13402</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-7047</v>
+        <v>-7188</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -911,7 +911,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-665</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6632</v>
+        <v>6633</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11076</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4444</v>
+        <v>-4443</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>20</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>7821</v>
+        <v>6214</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>11076</v>
+        <v>16713</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-3255</v>
+        <v>-10499</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
         <v>6214</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16699</v>
+        <v>16713</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-10485</v>
+        <v>-10499</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16699</v>
+        <v>16713</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-10485</v>
+        <v>-8455</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>8258</v>
+        <v>6214</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>16699</v>
+        <v>13416</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-8441</v>
+        <v>-7202</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
         <v>6214</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-7188</v>
+        <v>-7202</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-7188</v>
+        <v>-7061</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6355</v>
+        <v>6214</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-7047</v>
+        <v>-7202</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>30</v>
@@ -956,17 +956,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
         <v>6214</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-7188</v>
+        <v>-7202</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6214</v>
+        <v>6355</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13402</v>
+        <v>13416</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7188</v>
+        <v>-7061</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,26 +1046,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>13402</v>
+        <v>12147</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-7047</v>
+        <v>-3889</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>8258</v>
+        <v>4298</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-3889</v>
+        <v>-7849</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
@@ -1226,26 +1226,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-5933</v>
+        <v>-3889</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-227</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>6355</v>
+        <v>8258</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-5792</v>
+        <v>-3889</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>EgyptAir MS-655</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>11-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>EgyptAir MS-643</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
         <v>8258</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>12147</v>
+        <v>9582</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-3889</v>
+        <v>-1324</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-176</t>
+          <t>EgyptAir MS-641</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>6214</v>
+        <v>8258</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9568</v>
+        <v>9582</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-3354</v>
+        <v>-1324</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>EgyptAir MS-669</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
         <v>8258</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>9568</v>
+        <v>9582</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-1310</v>
+        <v>-1324</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1568,51 +1568,6 @@
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-641</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>8258</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>9568</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>-1310</v>
-      </c>
-      <c r="G25" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H25" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>4298</v>
+        <v>6214</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>12147</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-7849</v>
+        <v>-5933</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6633</v>
+        <v>6630</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>11076</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4443</v>
+        <v>-4446</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>20</v>

--- a/excel_routes/route_ATZ_JED_threats.xlsx
+++ b/excel_routes/route_ATZ_JED_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -50,12 +50,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00D4EDDA"/>
         <bgColor rgb="00D4EDDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -83,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -95,9 +89,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -465,12 +456,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -541,7 +532,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +542,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-174</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>6214</v>
+        <v>6184</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11076</v>
+        <v>10219</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-4862</v>
+        <v>-4035</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>30</v>
@@ -586,7 +577,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>29-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,26 +587,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Air Arabia Egypt E5-327</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>6630</v>
+        <v>6184</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11076</v>
+        <v>10219</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-4446</v>
+        <v>-4035</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
@@ -641,17 +632,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>6214</v>
+        <v>6338</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16713</v>
+        <v>10219</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-10499</v>
+        <v>-3881</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>30</v>
@@ -662,9 +653,9 @@
       <c r="I4" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,17 +677,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>6214</v>
+        <v>6184</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16713</v>
+        <v>9563</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-10499</v>
+        <v>-3379</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>30</v>
@@ -707,9 +698,9 @@
       <c r="I5" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,30 +722,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16713</v>
+        <v>9563</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-8455</v>
+        <v>-3379</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +757,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,17 +767,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>6214</v>
+        <v>6338</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13416</v>
+        <v>9563</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-7202</v>
+        <v>-3225</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>30</v>
@@ -797,9 +788,9 @@
       <c r="I7" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -825,13 +816,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>6214</v>
+        <v>6184</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13416</v>
+        <v>12146</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-7202</v>
+        <v>-5962</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>30</v>
@@ -842,7 +833,7 @@
       <c r="I8" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="J8" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -870,13 +861,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>6355</v>
+        <v>6338</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13416</v>
+        <v>12146</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-7061</v>
+        <v>-5808</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>30</v>
@@ -887,7 +878,7 @@
       <c r="I9" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -901,7 +892,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>07-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,28 +902,28 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>EgyptAir MS-673</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>6214</v>
+        <v>8753</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>13416</v>
+        <v>12146</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-7202</v>
+        <v>-3393</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -956,17 +947,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-172</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>6214</v>
+        <v>6184</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>13416</v>
+        <v>13403</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-7202</v>
+        <v>-7219</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>30</v>
@@ -977,7 +968,7 @@
       <c r="I11" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1001,17 +992,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Nile Air NP-127</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>6355</v>
+        <v>6184</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>13416</v>
+        <v>13403</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-7061</v>
+        <v>-7219</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>30</v>
@@ -1022,7 +1013,7 @@
       <c r="I12" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1036,7 +1027,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>07-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,28 +1037,28 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>12147</v>
+        <v>13403</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-3889</v>
+        <v>-7065</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1091,28 +1082,28 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nesma Airlines NE-174</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-3889</v>
+        <v>-5962</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1136,28 +1127,28 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-327</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3889</v>
+        <v>-5808</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1171,7 +1162,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1172,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Nesma Airlines NE-170</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>6214</v>
+        <v>6338</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-5933</v>
+        <v>-5808</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>30</v>
@@ -1202,7 +1193,7 @@
       <c r="I16" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="J16" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1226,28 +1217,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nesma Airlines NE-170</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-3889</v>
+        <v>-5962</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1271,28 +1262,28 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-3889</v>
+        <v>-5808</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1306,7 +1297,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,28 +1307,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>8258</v>
+        <v>6338</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-3889</v>
+        <v>-5808</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1361,28 +1352,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>8258</v>
+        <v>5012</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-3889</v>
+        <v>-7134</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J20" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1406,28 +1397,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-655</t>
+          <t>Nile Air NP-127</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>8258</v>
+        <v>5012</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>12147</v>
+        <v>12146</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-3889</v>
+        <v>-7134</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1441,7 +1432,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>11-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1442,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-643</t>
+          <t>Nesma Airlines NE-172</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>8258</v>
+        <v>6184</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>9582</v>
+        <v>12146</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-1324</v>
+        <v>-5962</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J22" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1496,26 +1487,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-641</t>
+          <t>Nile Air NP-227</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>8258</v>
+        <v>5012</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>9582</v>
+        <v>8893</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-1324</v>
+        <v>-3881</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
@@ -1523,51 +1514,6 @@
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>EGP</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>11-JUN-26</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>SM-455</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-669</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>8258</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>9582</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>-1324</v>
-      </c>
-      <c r="G24" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H24" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>EGP</t>
         </is>
